--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/Мелитополь/дв 22,09,26 млрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/Мелитополь/дв 22,09,26 млрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\Создание расчетов\ПОКОМ_КИ_UK_Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F55111-E90A-4729-9F04-63957117D5A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F1823B-3503-472F-BCD2-BBC6A790A241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,20 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$128</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="178">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -555,13 +547,16 @@
     <t>БОНУС_615  Гречка по-купечески с говядиной и овощами 0,325кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
-    <t>итого</t>
-  </si>
-  <si>
     <t>дн</t>
   </si>
   <si>
     <t>недогр</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>27,09,</t>
   </si>
 </sst>
 </file>
@@ -1118,10 +1113,10 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>175</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>176</v>
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -1212,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>17</v>
@@ -1301,7 +1296,9 @@
         <v>27</v>
       </c>
       <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
+      <c r="V4" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1" t="s">
@@ -10451,7 +10448,7 @@
       </c>
       <c r="U87" s="5"/>
       <c r="V87" s="5">
-        <f t="shared" ref="V86:V88" si="34">U87+$V$1*T87</f>
+        <f t="shared" ref="V87" si="34">U87+$V$1*T87</f>
         <v>723.50464000000011</v>
       </c>
       <c r="W87" s="1">
